--- a/assets/files/nested_IF_untuk_grade.xlsx
+++ b/assets/files/nested_IF_untuk_grade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32CF1F1-3DFE-434B-90C7-513027AE7D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2173D05-151C-4ADF-B2F3-D069BE4CAEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{CA549601-A7AF-4200-B856-DEF35841F3CF}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CA549601-A7AF-4200-B856-DEF35841F3CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -344,9 +344,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -384,7 +384,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -490,7 +490,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -632,7 +632,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -641,14 +641,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA6F1795-B4D1-475B-AEAB-D5A81C0D3B74}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
     <col min="2" max="6" width="14.5703125" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>18</v>
       </c>
@@ -658,7 +658,7 @@
       <c r="E1" s="13"/>
       <c r="F1" s="14"/>
     </row>
-    <row r="2" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>1</v>
       </c>
@@ -700,7 +700,7 @@
         <v>Bonus</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -722,7 +722,7 @@
         <v>Bonus</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>3</v>
       </c>
@@ -744,7 +744,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>4</v>
       </c>
@@ -766,7 +766,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>5</v>
       </c>
@@ -788,7 +788,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>6</v>
       </c>
@@ -810,7 +810,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>7</v>
       </c>
@@ -832,7 +832,7 @@
         <v>Bonus</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>8</v>
       </c>
@@ -854,7 +854,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>9</v>
       </c>
@@ -876,7 +876,7 @@
         <v>Bonus</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>10</v>
       </c>
